--- a/miranda_bonus_chartQ13.xlsx
+++ b/miranda_bonus_chartQ13.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F22F33E8-F094-41B2-9481-371E71C80518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BE270E-216E-4D7D-83EF-8F505EF24C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{83F94563-6C32-4839-B94A-179D20B041ED}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -603,9 +603,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -690,6 +689,31 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TOTAL SALES BY REGION</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1033,20 +1057,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1103,20 +1114,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1173,20 +1171,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1243,18 +1228,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1311,18 +1285,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1379,20 +1342,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1449,20 +1399,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1519,24 +1456,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1593,24 +1513,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1667,24 +1570,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4202,7 +4088,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8DA2AA6-6BF0-47A1-AB7E-554319209070}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8DA2AA6-6BF0-47A1-AB7E-554319209070}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A1:L17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -4932,15 +4818,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -4978,332 +4864,212 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>2392222.44</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1">
+      <c r="I3">
         <v>4330817.09</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1">
+      <c r="L3">
         <v>6723039.5299999993</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>2392222.44</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1">
+      <c r="L4">
         <v>2392222.44</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1">
+      <c r="I5">
         <v>4330817.09</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1">
+      <c r="L5">
         <v>4330817.09</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>1877249.75</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>11451615.09</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>5733256.2699999996</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>5175405.87</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1">
+      <c r="L6">
         <v>24237526.98</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>5733256.2699999996</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>5733256.2699999996</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>1877249.75</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1">
+      <c r="L8">
         <v>1877249.75</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>5175405.87</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1">
+      <c r="L9">
         <v>5175405.87</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>11451615.09</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1">
+      <c r="L10">
         <v>11451615.09</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>3930187.55</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
+      <c r="J11">
         <v>648812.56000000006</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11">
         <v>3417850.01</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11">
         <v>7996850.1199999992</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1">
+      <c r="K12">
         <v>3417850.01</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>3417850.01</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>3930187.55</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1">
+      <c r="L13">
         <v>3930187.55</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1">
+      <c r="J14">
         <v>648812.56000000006</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1">
+      <c r="L14">
         <v>648812.56000000006</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>6412632.2199999997</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1">
+      <c r="L15">
         <v>6412632.2199999997</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>6412632.2199999997</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1">
+      <c r="L16">
         <v>6412632.2199999997</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>6412632.2199999997</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>2392222.44</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>3930187.55</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>1877249.75</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>11451615.09</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17">
         <v>5733256.2699999996</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>5175405.87</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17">
         <v>4330817.09</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17">
         <v>648812.56000000006</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17">
         <v>3417850.01</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17">
         <v>45370048.849999994</v>
       </c>
     </row>

--- a/miranda_bonus_chartQ13.xlsx
+++ b/miranda_bonus_chartQ13.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BE270E-216E-4D7D-83EF-8F505EF24C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21537869-F2F5-40F9-B5BE-8C3B27A13468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{83F94563-6C32-4839-B94A-179D20B041ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{83F94563-6C32-4839-B94A-179D20B041ED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="miranda_bonus_chartQ13" sheetId="1" r:id="rId2"/>
+    <sheet name="Detail1" sheetId="3" r:id="rId1"/>
+    <sheet name="PIVOTCHART" sheetId="2" r:id="rId2"/>
+    <sheet name="miranda_bonus_chartQ13" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="33">
   <si>
     <t>SalesManager</t>
   </si>
@@ -120,6 +121,9 @@
   </si>
   <si>
     <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Details for Sum of TotalRevenue</t>
   </si>
 </sst>
 </file>
@@ -603,7 +607,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -612,6 +616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -684,7 +689,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[miranda_bonus_chartQ13.xlsx]Sheet1!PivotTable1</c:name>
+    <c:name>[miranda_bonus_chartQ13.xlsx]PIVOTCHART!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1637,7 +1642,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1:$B$2</c:f>
+              <c:f>PIVOTCHART!$B$1:$B$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1715,7 +1720,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -1769,7 +1774,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$17</c:f>
+              <c:f>PIVOTCHART!$B$3:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1790,7 +1795,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1:$C$2</c:f>
+              <c:f>PIVOTCHART!$C$1:$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1868,7 +1873,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -1922,7 +1927,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$17</c:f>
+              <c:f>PIVOTCHART!$C$3:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1943,7 +1948,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$1:$D$2</c:f>
+              <c:f>PIVOTCHART!$D$1:$D$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2021,7 +2026,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2075,7 +2080,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$17</c:f>
+              <c:f>PIVOTCHART!$D$3:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2096,7 +2101,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1:$E$2</c:f>
+              <c:f>PIVOTCHART!$E$1:$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2174,7 +2179,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2228,7 +2233,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$17</c:f>
+              <c:f>PIVOTCHART!$E$3:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2249,7 +2254,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$1:$F$2</c:f>
+              <c:f>PIVOTCHART!$F$1:$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2327,7 +2332,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2381,7 +2386,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$17</c:f>
+              <c:f>PIVOTCHART!$F$3:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2402,7 +2407,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$1:$G$2</c:f>
+              <c:f>PIVOTCHART!$G$1:$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2480,7 +2485,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2534,7 +2539,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$17</c:f>
+              <c:f>PIVOTCHART!$G$3:$G$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2555,7 +2560,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$1:$H$2</c:f>
+              <c:f>PIVOTCHART!$H$1:$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2635,7 +2640,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2689,7 +2694,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$17</c:f>
+              <c:f>PIVOTCHART!$H$3:$H$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2710,7 +2715,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$1:$I$2</c:f>
+              <c:f>PIVOTCHART!$I$1:$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2790,7 +2795,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2844,7 +2849,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$17</c:f>
+              <c:f>PIVOTCHART!$I$3:$I$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2865,7 +2870,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$1:$J$2</c:f>
+              <c:f>PIVOTCHART!$J$1:$J$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2945,7 +2950,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -2999,7 +3004,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$17</c:f>
+              <c:f>PIVOTCHART!$J$3:$J$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3020,7 +3025,7 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$1:$K$2</c:f>
+              <c:f>PIVOTCHART!$K$1:$K$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3100,7 +3105,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$A$17</c:f>
+              <c:f>PIVOTCHART!$A$3:$A$17</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="10"/>
                 <c:lvl>
@@ -3154,7 +3159,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$17</c:f>
+              <c:f>PIVOTCHART!$K$3:$K$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4475,6 +4480,19 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D900F2E-27E9-4996-B636-5E55B85CA186}" name="Table1" displayName="Table1" ref="A3:D13" totalsRowShown="0">
+  <autoFilter ref="A3:D13" xr:uid="{4D900F2E-27E9-4996-B636-5E55B85CA186}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5A0A167F-5F29-4359-B297-D40A9EEECC88}" name="SalesManager"/>
+    <tableColumn id="2" xr3:uid="{F3C993F0-9305-40E6-9B29-26ADB25DE763}" name="State"/>
+    <tableColumn id="3" xr3:uid="{8E1EC976-68C8-4FB7-BBFE-FCE95D6F0561}" name="Region"/>
+    <tableColumn id="4" xr3:uid="{8EC9F2E6-59F2-4189-A229-11821E0DCAD5}" name="TotalRevenue"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4791,6 +4809,184 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D660726A-9448-4169-83A9-86A754D7FB76}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>5733256.2699999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>2392222.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>1877249.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>3417850.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>6412632.2199999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>3930187.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>648812.56000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>5175405.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>4330817.09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>11451615.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678FDE8B-9904-4A1B-85C6-5050F29CDE29}">
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5079,7 +5275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499DDB63-0A66-43A3-8550-5881E938F726}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="18.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
